--- a/numerical-workflows/v2/framework/06_最终配置/房车/RvLvUp.xlsx
+++ b/numerical-workflows/v2/framework/06_最终配置/房车/RvLvUp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RvLvUp" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="中文说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RvLvUp" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中文说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RvLvUp'!$A$4:$E$103</definedName>
@@ -610,7 +610,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>600</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="6">
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>700</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="7">
@@ -638,7 +638,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>800</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="8">
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1000</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="9">
@@ -666,7 +666,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1100</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="10">
@@ -680,7 +680,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1300</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="11">
@@ -694,7 +694,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1400</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="12">
@@ -708,7 +708,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1500</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="13">
@@ -722,7 +722,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1700</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="14">
@@ -736,7 +736,7 @@
         <v>14</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="15">
@@ -750,7 +750,7 @@
         <v>16</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2200</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="16">
@@ -764,7 +764,7 @@
         <v>18</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2500</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="17">
@@ -778,7 +778,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2800</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="18">
@@ -792,7 +792,7 @@
         <v>22</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>3100</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="19">
@@ -806,7 +806,7 @@
         <v>24</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>3400</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="20">
@@ -820,7 +820,7 @@
         <v>26</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3600</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="21">
@@ -834,7 +834,7 @@
         <v>28</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>3900</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="22">
@@ -848,7 +848,7 @@
         <v>30</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>4200</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="23">
@@ -862,7 +862,7 @@
         <v>32</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4500</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="24">
@@ -876,7 +876,7 @@
         <v>34</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>4800</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="25">
@@ -890,7 +890,7 @@
         <v>36</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5000</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="26">
@@ -904,7 +904,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5300</v>
+        <v>7400</v>
       </c>
     </row>
     <row r="27">
@@ -918,7 +918,7 @@
         <v>40</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5600</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="28">
@@ -932,7 +932,7 @@
         <v>42</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>5900</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="29">
@@ -946,7 +946,7 @@
         <v>46</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="30">
@@ -960,7 +960,7 @@
         <v>49</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6900</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="31">
@@ -974,7 +974,7 @@
         <v>52</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>7300</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="32">
@@ -988,7 +988,7 @@
         <v>55</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>7700</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="33">
